--- a/알고리즘 계획표.xlsx
+++ b/알고리즘 계획표.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\JAVA\projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB262678-F531-4F3A-8761-C04019FB380D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36842EA6-FCE4-42B3-B982-184B5BFD842C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -970,20 +970,20 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1330,17 +1330,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="96" customHeight="1">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="20"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" s="1" t="s">
@@ -1370,13 +1370,13 @@
       <c r="I2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="J2" s="22" t="s">
+      <c r="J2" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="22"/>
+      <c r="K2" s="19"/>
     </row>
     <row r="3" spans="1:11" ht="33">
-      <c r="A3" s="19" t="s">
+      <c r="A3" s="20" t="s">
         <v>5</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -1405,7 +1405,7 @@
       <c r="K3" s="9"/>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="19"/>
+      <c r="A4" s="20"/>
       <c r="B4" s="8" t="s">
         <v>89</v>
       </c>
@@ -1430,8 +1430,8 @@
       <c r="K4" s="9"/>
     </row>
     <row r="5" spans="1:11">
-      <c r="A5" s="19"/>
-      <c r="B5" s="19" t="s">
+      <c r="A5" s="20"/>
+      <c r="B5" s="20" t="s">
         <v>40</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -1463,8 +1463,8 @@
       </c>
     </row>
     <row r="6" spans="1:11">
-      <c r="A6" s="19"/>
-      <c r="B6" s="19"/>
+      <c r="A6" s="20"/>
+      <c r="B6" s="20"/>
       <c r="C6" s="2" t="s">
         <v>15</v>
       </c>
@@ -1494,8 +1494,8 @@
       </c>
     </row>
     <row r="7" spans="1:11">
-      <c r="A7" s="19"/>
-      <c r="B7" s="19"/>
+      <c r="A7" s="20"/>
+      <c r="B7" s="20"/>
       <c r="C7" s="2" t="s">
         <v>14</v>
       </c>
@@ -1525,8 +1525,8 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="33">
-      <c r="A8" s="19"/>
-      <c r="B8" s="19"/>
+      <c r="A8" s="20"/>
+      <c r="B8" s="20"/>
       <c r="C8" s="7" t="s">
         <v>39</v>
       </c>
@@ -1556,8 +1556,8 @@
       </c>
     </row>
     <row r="9" spans="1:11">
-      <c r="A9" s="19"/>
-      <c r="B9" s="19"/>
+      <c r="A9" s="20"/>
+      <c r="B9" s="20"/>
       <c r="C9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1584,8 +1584,8 @@
       </c>
     </row>
     <row r="10" spans="1:11">
-      <c r="A10" s="19"/>
-      <c r="B10" s="19"/>
+      <c r="A10" s="20"/>
+      <c r="B10" s="20"/>
       <c r="C10" s="2" t="s">
         <v>76</v>
       </c>
@@ -1610,8 +1610,8 @@
       <c r="J10" s="2"/>
     </row>
     <row r="11" spans="1:11" ht="33">
-      <c r="A11" s="19"/>
-      <c r="B11" s="19"/>
+      <c r="A11" s="20"/>
+      <c r="B11" s="20"/>
       <c r="C11" s="7" t="s">
         <v>79</v>
       </c>
@@ -1634,7 +1634,7 @@
       <c r="J11" s="2"/>
     </row>
     <row r="12" spans="1:11">
-      <c r="A12" s="19"/>
+      <c r="A12" s="20"/>
       <c r="B12" s="2" t="s">
         <v>41</v>
       </c>
@@ -1664,7 +1664,7 @@
       </c>
     </row>
     <row r="13" spans="1:11">
-      <c r="A13" s="19"/>
+      <c r="A13" s="20"/>
       <c r="B13" s="2" t="s">
         <v>42</v>
       </c>
@@ -1688,10 +1688,10 @@
       </c>
     </row>
     <row r="14" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A14" s="19" t="s">
+      <c r="A14" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="21" t="s">
         <v>84</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -1723,8 +1723,8 @@
       </c>
     </row>
     <row r="15" spans="1:11">
-      <c r="A15" s="19"/>
-      <c r="B15" s="23"/>
+      <c r="A15" s="20"/>
+      <c r="B15" s="21"/>
       <c r="C15" s="2" t="s">
         <v>32</v>
       </c>
@@ -1754,8 +1754,8 @@
       </c>
     </row>
     <row r="16" spans="1:11">
-      <c r="A16" s="19"/>
-      <c r="B16" s="23"/>
+      <c r="A16" s="20"/>
+      <c r="B16" s="21"/>
       <c r="C16" s="2" t="s">
         <v>33</v>
       </c>
@@ -1785,8 +1785,8 @@
       </c>
     </row>
     <row r="17" spans="1:11">
-      <c r="A17" s="19"/>
-      <c r="B17" s="23"/>
+      <c r="A17" s="20"/>
+      <c r="B17" s="21"/>
       <c r="C17" s="2" t="s">
         <v>35</v>
       </c>
@@ -1816,8 +1816,8 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="49.5">
-      <c r="A18" s="19"/>
-      <c r="B18" s="23"/>
+      <c r="A18" s="20"/>
+      <c r="B18" s="21"/>
       <c r="C18" s="7" t="s">
         <v>48</v>
       </c>
@@ -1842,8 +1842,8 @@
       <c r="J18" s="9"/>
     </row>
     <row r="19" spans="1:11" ht="33">
-      <c r="A19" s="19"/>
-      <c r="B19" s="23"/>
+      <c r="A19" s="20"/>
+      <c r="B19" s="21"/>
       <c r="C19" s="7" t="s">
         <v>53</v>
       </c>
@@ -1870,8 +1870,8 @@
       </c>
     </row>
     <row r="20" spans="1:11">
-      <c r="A20" s="19"/>
-      <c r="B20" s="23"/>
+      <c r="A20" s="20"/>
+      <c r="B20" s="21"/>
       <c r="C20" s="2" t="s">
         <v>50</v>
       </c>
@@ -1895,8 +1895,8 @@
       </c>
     </row>
     <row r="21" spans="1:11" ht="33">
-      <c r="A21" s="19"/>
-      <c r="B21" s="23"/>
+      <c r="A21" s="20"/>
+      <c r="B21" s="21"/>
       <c r="C21" s="7" t="s">
         <v>54</v>
       </c>
@@ -1923,8 +1923,8 @@
       </c>
     </row>
     <row r="22" spans="1:11">
-      <c r="A22" s="19"/>
-      <c r="B22" s="23"/>
+      <c r="A22" s="20"/>
+      <c r="B22" s="21"/>
       <c r="C22" s="7">
         <v>4963</v>
       </c>
@@ -1946,10 +1946,13 @@
       <c r="I22" s="2">
         <v>241007</v>
       </c>
+      <c r="J22" s="8">
+        <v>241022</v>
+      </c>
     </row>
     <row r="23" spans="1:11">
-      <c r="A23" s="19"/>
-      <c r="B23" s="23"/>
+      <c r="A23" s="20"/>
+      <c r="B23" s="21"/>
       <c r="C23" s="7" t="s">
         <v>85</v>
       </c>
@@ -1969,10 +1972,10 @@
       <c r="I23" s="8"/>
     </row>
     <row r="24" spans="1:11" ht="33">
-      <c r="A24" s="19" t="s">
+      <c r="A24" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="19" t="s">
+      <c r="B24" s="20" t="s">
         <v>37</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -2001,8 +2004,8 @@
       </c>
     </row>
     <row r="25" spans="1:11">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
+      <c r="A25" s="20"/>
+      <c r="B25" s="20"/>
       <c r="C25" s="2" t="s">
         <v>44</v>
       </c>
@@ -2021,8 +2024,8 @@
       <c r="H25" s="8"/>
     </row>
     <row r="26" spans="1:11">
-      <c r="A26" s="19"/>
-      <c r="B26" s="19"/>
+      <c r="A26" s="20"/>
+      <c r="B26" s="20"/>
       <c r="C26" s="2" t="s">
         <v>46</v>
       </c>
@@ -2049,8 +2052,8 @@
       </c>
     </row>
     <row r="27" spans="1:11">
-      <c r="A27" s="19"/>
-      <c r="B27" s="19"/>
+      <c r="A27" s="20"/>
+      <c r="B27" s="20"/>
       <c r="C27" s="2" t="s">
         <v>47</v>
       </c>
@@ -2065,10 +2068,10 @@
       <c r="H27" s="8"/>
     </row>
     <row r="28" spans="1:11">
-      <c r="A28" s="19" t="s">
+      <c r="A28" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="19" t="s">
+      <c r="B28" s="20" t="s">
         <v>49</v>
       </c>
       <c r="C28" s="2">
@@ -2092,8 +2095,8 @@
       <c r="I28" s="8"/>
     </row>
     <row r="29" spans="1:11">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
+      <c r="A29" s="20"/>
+      <c r="B29" s="20"/>
       <c r="C29" s="2" t="s">
         <v>52</v>
       </c>
@@ -2117,8 +2120,8 @@
       </c>
     </row>
     <row r="30" spans="1:11">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
+      <c r="A30" s="20"/>
+      <c r="B30" s="20"/>
       <c r="C30" s="2" t="s">
         <v>80</v>
       </c>
@@ -2147,7 +2150,7 @@
       </c>
     </row>
     <row r="32" spans="1:11">
-      <c r="A32" s="19" t="s">
+      <c r="A32" s="20" t="s">
         <v>65</v>
       </c>
       <c r="B32" s="2" t="s">
@@ -2176,8 +2179,8 @@
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" s="19"/>
-      <c r="B33" s="19" t="s">
+      <c r="A33" s="20"/>
+      <c r="B33" s="20" t="s">
         <v>75</v>
       </c>
       <c r="C33" s="2" t="s">
@@ -2203,8 +2206,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" ht="33">
-      <c r="A34" s="19"/>
-      <c r="B34" s="19"/>
+      <c r="A34" s="20"/>
+      <c r="B34" s="20"/>
       <c r="C34" s="7" t="s">
         <v>88</v>
       </c>
@@ -2228,7 +2231,7 @@
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" s="19"/>
+      <c r="A35" s="20"/>
       <c r="B35" s="2" t="s">
         <v>90</v>
       </c>
@@ -2248,7 +2251,7 @@
       <c r="H35" s="8"/>
     </row>
     <row r="36" spans="1:9">
-      <c r="A36" s="19"/>
+      <c r="A36" s="20"/>
       <c r="B36" s="2" t="s">
         <v>82</v>
       </c>
@@ -2272,10 +2275,10 @@
       </c>
     </row>
     <row r="37" spans="1:9">
-      <c r="A37" s="19" t="s">
+      <c r="A37" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="B37" s="19" t="s">
+      <c r="B37" s="20" t="s">
         <v>77</v>
       </c>
       <c r="C37" s="2" t="s">
@@ -2298,8 +2301,8 @@
       </c>
     </row>
     <row r="38" spans="1:9">
-      <c r="A38" s="19"/>
-      <c r="B38" s="19"/>
+      <c r="A38" s="20"/>
+      <c r="B38" s="20"/>
       <c r="C38" s="2" t="s">
         <v>81</v>
       </c>
@@ -2321,6 +2324,12 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="A37:A38"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="B33:B34"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="A3:A13"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="A24:A27"/>
     <mergeCell ref="B24:B27"/>
@@ -2329,12 +2338,6 @@
     <mergeCell ref="B28:B30"/>
     <mergeCell ref="A14:A23"/>
     <mergeCell ref="B14:B23"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="A37:A38"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="B33:B34"/>
-    <mergeCell ref="A32:A36"/>
-    <mergeCell ref="A3:A13"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2395,7 +2398,7 @@
       <c r="B3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="C3" s="19"/>
+      <c r="C3" s="20"/>
       <c r="D3" s="11" t="s">
         <v>61</v>
       </c>
